--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 05/02. Trả bảo hành/TBH_Victory_260526.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 05/02. Trả bảo hành/TBH_Victory_260526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 05\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB39428-D811-40DC-B0A0-F9B326599697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BDA92D-BEA9-419E-813E-C8316BDCED8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="P.TraBaoHanh" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">P.TraBaoHanh!$A$1:$I$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">P.TraBaoHanh!$A$1:$I$23</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -100,16 +100,45 @@
     <t>Mất cấu hình</t>
   </si>
   <si>
-    <t>Cấu hình test lại thiết bị</t>
-  </si>
-  <si>
-    <t>Hà Nội, ngày 26  tháng 05  năm 2026</t>
-  </si>
-  <si>
     <t>Khách hàng/ người đại diện: Đại lý Victory</t>
   </si>
   <si>
     <t>003200B10F</t>
+  </si>
+  <si>
+    <t>0032002826</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>Chưa xác định được lỗi</t>
+  </si>
+  <si>
+    <t>Test lại thiết bị</t>
+  </si>
+  <si>
+    <t>Xử lý lại connector module GPS</t>
+  </si>
+  <si>
+    <t>0032002A2F</t>
+  </si>
+  <si>
+    <t>Hà Nội, ngày 26 tháng 05 năm 2026</t>
+  </si>
+  <si>
+    <t>Thẻ nhớ lỗi, trả kèm một thẻ nhớ mới lắp trong thiết bị</t>
+  </si>
+  <si>
+    <t>Mất giao tiếp 
+module GPS</t>
+  </si>
+  <si>
+    <t>Cấu hình test 
+lại thiết bị</t>
+  </si>
+  <si>
+    <t>Hết BH</t>
   </si>
 </sst>
 </file>
@@ -119,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,13 +249,7 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -370,7 +393,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -447,28 +470,25 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -504,26 +524,32 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -888,7 +914,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="5" customWidth="1"/>
@@ -896,7 +922,7 @@
     <col min="3" max="3" width="16.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.28515625" style="3" customWidth="1"/>
     <col min="8" max="8" width="19" style="2" customWidth="1"/>
     <col min="9" max="9" width="14" style="4" customWidth="1"/>
@@ -906,92 +932,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40"/>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41" t="s">
+      <c r="A1" s="39"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="42" t="s">
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="44"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="45" t="s">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="47"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="48" t="s">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="50"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
+      <c r="A6" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="22"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
       <c r="I6" s="31" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="22"/>
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
@@ -999,12 +1025,12 @@
       <c r="I7" s="21"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="22"/>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
@@ -1012,12 +1038,12 @@
       <c r="I8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="22"/>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
@@ -1025,135 +1051,167 @@
       <c r="I9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="58" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32">
+      <c r="A11" s="50">
         <v>1</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="E11" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="54"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50">
+        <v>2</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E12" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="54"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="50">
+        <v>3</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="33" t="s">
+      <c r="F13" s="51"/>
+      <c r="G13" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="26"/>
+      <c r="H13" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="54"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="26"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="55" t="s">
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56" t="s">
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="56" t="s">
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="56"/>
-      <c r="I15" s="56"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="9"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
     </row>
     <row r="18" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28"/>
@@ -1161,72 +1219,94 @@
       <c r="C18" s="14"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
-      <c r="F18" s="6"/>
+      <c r="F18" s="13"/>
       <c r="G18" s="29"/>
       <c r="H18" s="8"/>
       <c r="I18" s="9"/>
     </row>
     <row r="19" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="17"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="28"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="9"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="27"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="57" t="s">
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="19"/>
-    </row>
-    <row r="23" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-    </row>
-    <row r="62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="19"/>
+    </row>
+    <row r="25" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+    </row>
+    <row r="64" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="D3:I3"/>
     <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A22:D22"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
